--- a/data/trans_orig/IP04D$notiene-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$notiene-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19433</t>
+          <t>19745</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30831</t>
+          <t>29931</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42169</t>
+          <t>42644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51278</t>
+          <t>51087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45376</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>56460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90436</t>
+          <t>91336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105329</t>
+          <t>105650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15380</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24957</t>
+          <t>25144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88688</t>
+          <t>88887</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99186</t>
+          <t>99177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96496</t>
+          <t>96137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105631</t>
+          <t>105570</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188988</t>
+          <t>188801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>202704</t>
+          <t>203025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64104</t>
+          <t>64537</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67676</t>
+          <t>68036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134393</t>
+          <t>134368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72279</t>
+          <t>71996</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77121</t>
+          <t>77142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154456</t>
+          <t>154433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159365</t>
+          <t>159364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9566</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37400</t>
+          <t>37633</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43192</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40494</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46067</t>
+          <t>46068</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81087</t>
+          <t>81602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88941</t>
+          <t>89026</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>132626</t>
+          <t>132713</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138054</t>
+          <t>138067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137120</t>
+          <t>137007</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144146</t>
+          <t>143840</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>272980</t>
+          <t>272967</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>281245</t>
+          <t>281184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>156896</t>
+          <t>155593</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>162597</t>
+          <t>162695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>164825</t>
+          <t>165620</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>170690</t>
+          <t>170692</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>325064</t>
+          <t>324729</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>332571</t>
+          <t>332596</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39146</t>
+          <t>37967</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41019</t>
+          <t>42082</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47894</t>
+          <t>47059</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74764</t>
+          <t>72732</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>669146</t>
+          <t>670325</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>686963</t>
+          <t>687544</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>711206</t>
+          <t>710143</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>729919</t>
+          <t>730041</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1385753</t>
+          <t>1387785</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1412623</t>
+          <t>1413458</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>29836</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26739</t>
+          <t>27380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39844</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46939</t>
+          <t>47715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>64796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28474</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40352</t>
+          <t>40078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24618</t>
+          <t>24193</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37723</t>
+          <t>37082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57121</t>
+          <t>57037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74894</t>
+          <t>74118</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16824</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30683</t>
+          <t>30953</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38574</t>
+          <t>37771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>44020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66071</t>
+          <t>64427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73264</t>
+          <t>72994</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87123</t>
+          <t>86829</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71709</t>
+          <t>72512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86810</t>
+          <t>86906</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148159</t>
+          <t>149803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>170518</t>
+          <t>170210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60579</t>
+          <t>60379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66134</t>
+          <t>66145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66537</t>
+          <t>66551</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129728</t>
+          <t>129625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136003</t>
+          <t>135969</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70170</t>
+          <t>70792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75568</t>
+          <t>75572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70143</t>
+          <t>69270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78780</t>
+          <t>78703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142682</t>
+          <t>143071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153372</t>
+          <t>153290</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84212</t>
+          <t>84225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20131</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21124</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22377</t>
+          <t>22057</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>37608</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34142</t>
+          <t>34250</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>44471</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36615</t>
+          <t>36196</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48103</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73474</t>
+          <t>74404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89635</t>
+          <t>89955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19551</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34752</t>
+          <t>34732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31010</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40110</t>
+          <t>39540</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59440</t>
+          <t>61324</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101850</t>
+          <t>101870</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117051</t>
+          <t>116487</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108900</t>
+          <t>109174</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>123435</t>
+          <t>123060</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>217072</t>
+          <t>215188</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>236402</t>
+          <t>236972</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161329</t>
+          <t>161328</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>164581</t>
+          <t>164638</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>169552</t>
+          <t>169553</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>327763</t>
+          <t>327868</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>333680</t>
+          <t>333626</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78140</t>
+          <t>79563</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>107958</t>
+          <t>105936</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>95798</t>
+          <t>96101</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131128</t>
+          <t>128502</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>182313</t>
+          <t>181435</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>228599</t>
+          <t>227202</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>592223</t>
+          <t>594245</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>622041</t>
+          <t>620618</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>608883</t>
+          <t>611509</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>644213</t>
+          <t>643910</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1211593</t>
+          <t>1212990</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1257879</t>
+          <t>1258757</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23126</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43252</t>
+          <t>43138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28486</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>39382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66333</t>
+          <t>66996</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,89%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>30144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50297</t>
+          <t>50156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50880</t>
+          <t>51264</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>66004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86315</t>
+          <t>85652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112913</t>
+          <t>113266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>21425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30803</t>
+          <t>30115</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114573</t>
+          <t>114665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125337</t>
+          <t>125320</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106260</t>
+          <t>106171</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119687</t>
+          <t>119986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>224447</t>
+          <t>225135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>242708</t>
+          <t>243288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53744</t>
+          <t>53419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61965</t>
+          <t>62156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66777</t>
+          <t>66787</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118715</t>
+          <t>118295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124503</t>
+          <t>124289</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>62498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69812</t>
+          <t>68041</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77601</t>
+          <t>77583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136014</t>
+          <t>136601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145781</t>
+          <t>145785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>40611</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45655</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53614</t>
+          <t>51715</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97084</t>
+          <t>97078</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101811</t>
+          <t>101791</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>35147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>53322</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51793</t>
+          <t>49832</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78839</t>
+          <t>78732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91450</t>
+          <t>92867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124964</t>
+          <t>125380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72487</t>
+          <t>71186</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>90686</t>
+          <t>89361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>76230</t>
+          <t>76337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>103276</t>
+          <t>105237</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>154613</t>
+          <t>154197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>188127</t>
+          <t>186710</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,78%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123957</t>
+          <t>123611</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130347</t>
+          <t>130094</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149108</t>
+          <t>149075</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155369</t>
+          <t>155364</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>276027</t>
+          <t>275456</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>284646</t>
+          <t>284537</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>72945</t>
+          <t>71831</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>110824</t>
+          <t>111837</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86163</t>
+          <t>85913</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>130400</t>
+          <t>128326</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>168093</t>
+          <t>168616</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>229820</t>
+          <t>228630</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>554332</t>
+          <t>553319</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>592211</t>
+          <t>593325</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>629922</t>
+          <t>631996</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>674159</t>
+          <t>674409</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1195657</t>
+          <t>1196847</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1257384</t>
+          <t>1256861</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
